--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-microbiology.xlsx
@@ -628,7 +628,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -915,6 +915,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="18725-2"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -931,9 +939,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -4792,7 +4797,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5557,7 +5562,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5631,7 +5636,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>206</v>
@@ -5749,7 +5754,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>213</v>
@@ -5869,7 +5874,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>219</v>
@@ -5991,7 +5996,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>229</v>
@@ -6109,7 +6114,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>231</v>
@@ -6229,7 +6234,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>233</v>
@@ -6240,7 +6245,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6274,7 +6279,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -7686,7 +7691,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-microbiology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -653,6 +653,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="laboratory"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -807,9 +815,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>laboratory</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -947,9 +952,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>18725-2</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -1224,7 +1226,7 @@
     <t>このObservationの対象となる患者や患者群、機器、場所に関する情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1579,7 +1581,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -4116,7 +4118,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4135,7 +4137,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4188,10 +4190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4214,13 +4216,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4271,7 +4273,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4295,7 +4297,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4306,10 +4308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4338,7 +4340,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4379,10 +4381,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4391,7 +4393,7 @@
         <v>197</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4415,7 +4417,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4426,10 +4428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4452,19 +4454,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4513,7 +4515,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4534,10 +4536,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4548,10 +4550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4574,13 +4576,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4631,7 +4633,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4655,7 +4657,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4666,10 +4668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4698,7 +4700,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4739,10 +4741,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4751,7 +4753,7 @@
         <v>197</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4775,7 +4777,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4786,10 +4788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4815,23 +4817,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4873,7 +4875,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4894,10 +4896,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4908,10 +4910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4934,16 +4936,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4993,7 +4995,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5014,10 +5016,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5028,10 +5030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5057,21 +5059,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5174,7 +5176,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -5416,7 +5418,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>279</v>
@@ -5639,7 +5641,7 @@
         <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5662,13 +5664,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5719,7 +5721,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5743,7 +5745,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5757,7 +5759,7 @@
         <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5786,7 +5788,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5827,10 +5829,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5839,7 +5841,7 @@
         <v>197</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5863,7 +5865,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5877,7 +5879,7 @@
         <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5900,19 +5902,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5961,7 +5963,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5982,10 +5984,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5999,7 +6001,7 @@
         <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6022,13 +6024,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6079,7 +6081,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6103,7 +6105,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6117,7 +6119,7 @@
         <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6146,7 +6148,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6187,10 +6189,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6199,7 +6201,7 @@
         <v>197</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6223,7 +6225,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6237,7 +6239,7 @@
         <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6263,16 +6265,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6321,7 +6323,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6342,10 +6344,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6359,7 +6361,7 @@
         <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6382,16 +6384,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6441,7 +6443,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6462,10 +6464,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6479,7 +6481,7 @@
         <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6505,21 +6507,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6596,7 +6598,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>260</v>
@@ -6622,7 +6624,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>261</v>
@@ -6642,7 +6644,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -6716,7 +6718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>268</v>
@@ -6838,7 +6840,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>278</v>
@@ -6864,7 +6866,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>279</v>
@@ -6960,13 +6962,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6991,10 +6993,10 @@
         <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>289</v>
@@ -7029,7 +7031,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7082,10 +7084,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7108,13 +7110,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7165,7 +7167,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7189,7 +7191,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7200,10 +7202,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7232,7 +7234,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7273,10 +7275,10 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
@@ -7285,7 +7287,7 @@
         <v>197</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7309,7 +7311,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7320,10 +7322,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7346,19 +7348,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7407,7 +7409,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7428,10 +7430,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7442,10 +7444,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7468,13 +7470,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7525,7 +7527,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7549,7 +7551,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7560,10 +7562,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7592,7 +7594,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7633,10 +7635,10 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
@@ -7645,7 +7647,7 @@
         <v>197</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7669,7 +7671,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7680,10 +7682,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7709,23 +7711,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7767,7 +7769,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7788,10 +7790,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7802,10 +7804,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7828,16 +7830,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7887,7 +7889,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7908,10 +7910,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7922,10 +7924,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7951,14 +7953,14 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8042,7 +8044,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>260</v>
@@ -8068,7 +8070,7 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>261</v>
@@ -8162,7 +8164,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>268</v>
@@ -8284,7 +8286,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>278</v>
@@ -8310,7 +8312,7 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>279</v>
@@ -8406,14 +8408,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8435,16 +8437,16 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8469,14 +8471,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y52" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y52" t="s" s="2">
+      <c r="Z52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8493,7 +8495,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8508,30 +8510,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8554,13 +8556,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8611,7 +8613,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8635,7 +8637,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8646,10 +8648,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8678,7 +8680,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8719,10 +8721,10 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
@@ -8731,7 +8733,7 @@
         <v>197</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8755,7 +8757,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8766,10 +8768,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8792,19 +8794,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8841,7 +8843,7 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8851,7 +8853,7 @@
         <v>197</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8872,10 +8874,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8886,13 +8888,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>83</v>
@@ -8914,19 +8916,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="O56" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8955,7 +8957,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8973,7 +8975,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8994,10 +8996,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9008,10 +9010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9034,13 +9036,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9091,7 +9093,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9115,7 +9117,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9126,10 +9128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9158,7 +9160,7 @@
         <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9199,10 +9201,10 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
@@ -9211,7 +9213,7 @@
         <v>197</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9235,7 +9237,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9246,10 +9248,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9275,23 +9277,23 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9333,7 +9335,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9354,10 +9356,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9368,10 +9370,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9394,16 +9396,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9453,7 +9455,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9474,10 +9476,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9488,10 +9490,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9517,14 +9519,14 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9608,10 +9610,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9634,7 +9636,7 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>261</v>
@@ -9728,10 +9730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9850,13 +9852,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>83</v>
@@ -9878,19 +9880,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="O64" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9919,7 +9921,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9937,7 +9939,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9958,10 +9960,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9972,10 +9974,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9998,13 +10000,13 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10055,7 +10057,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10079,7 +10081,7 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10090,10 +10092,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10122,7 +10124,7 @@
         <v>141</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10163,10 +10165,10 @@
         <v>83</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>83</v>
@@ -10175,7 +10177,7 @@
         <v>197</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10199,7 +10201,7 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10210,10 +10212,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10239,23 +10241,23 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -10297,7 +10299,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10318,10 +10320,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10332,10 +10334,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10358,16 +10360,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10417,7 +10419,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10438,10 +10440,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10452,10 +10454,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10481,14 +10483,14 @@
         <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10572,10 +10574,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10598,7 +10600,7 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>261</v>
@@ -10692,10 +10694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10814,13 +10816,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C72" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>83</v>
@@ -10842,19 +10844,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="O72" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10883,7 +10885,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10901,7 +10903,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10922,10 +10924,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10936,10 +10938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10962,13 +10964,13 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11019,7 +11021,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11043,7 +11045,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11054,10 +11056,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11086,7 +11088,7 @@
         <v>141</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -11127,10 +11129,10 @@
         <v>83</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>83</v>
@@ -11139,7 +11141,7 @@
         <v>197</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11163,7 +11165,7 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11174,10 +11176,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11203,23 +11205,23 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>83</v>
@@ -11261,7 +11263,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11282,10 +11284,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11296,10 +11298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11322,16 +11324,16 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11381,7 +11383,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11402,10 +11404,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11416,10 +11418,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11445,14 +11447,14 @@
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11536,10 +11538,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11562,7 +11564,7 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>261</v>
@@ -11656,10 +11658,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11778,10 +11780,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11804,7 +11806,7 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>279</v>
@@ -11900,10 +11902,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11926,19 +11928,19 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11987,7 +11989,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12002,19 +12004,19 @@
         <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12022,10 +12024,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12048,16 +12050,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12107,7 +12109,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12128,13 +12130,13 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12142,14 +12144,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12168,19 +12170,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12229,7 +12231,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12244,19 +12246,19 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AL83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12264,14 +12266,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12290,19 +12292,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12351,7 +12353,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12366,19 +12368,19 @@
         <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12386,10 +12388,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12412,16 +12414,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12471,7 +12473,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12492,13 +12494,13 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -12506,10 +12508,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12532,19 +12534,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12593,7 +12595,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12608,19 +12610,19 @@
         <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AL86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -12628,10 +12630,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12654,19 +12656,19 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12715,7 +12717,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12724,7 +12726,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -12733,27 +12735,27 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12779,16 +12781,16 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12813,14 +12815,14 @@
         <v>83</v>
       </c>
       <c r="X88" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Y88" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="Y88" t="s" s="2">
+      <c r="Z88" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
       </c>
@@ -12837,7 +12839,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12846,7 +12848,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12861,7 +12863,7 @@
         <v>137</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12872,14 +12874,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12901,16 +12903,16 @@
         <v>190</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12935,14 +12937,14 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
       </c>
@@ -12959,7 +12961,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12977,27 +12979,27 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13020,19 +13022,19 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13081,7 +13083,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13102,10 +13104,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13116,10 +13118,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13145,13 +13147,13 @@
         <v>190</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13177,14 +13179,14 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13201,7 +13203,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13219,27 +13221,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM91" t="s" s="2">
+      <c r="AN91" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP91" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13265,16 +13267,16 @@
         <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13299,14 +13301,14 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13323,7 +13325,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13344,10 +13346,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13358,10 +13360,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13384,16 +13386,16 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13443,7 +13445,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13461,27 +13463,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13504,16 +13506,16 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13563,7 +13565,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13581,27 +13583,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>505</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13624,19 +13626,19 @@
         <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13685,7 +13687,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13697,19 +13699,19 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AK95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13720,10 +13722,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13746,13 +13748,13 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13803,7 +13805,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13827,7 +13829,7 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13838,10 +13840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13870,7 +13872,7 @@
         <v>141</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>143</v>
@@ -13923,7 +13925,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13947,7 +13949,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13958,14 +13960,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13987,10 +13989,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14045,7 +14047,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14080,10 +14082,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14106,13 +14108,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14163,7 +14165,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14172,7 +14174,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14184,10 +14186,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14198,10 +14200,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14224,13 +14226,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14281,7 +14283,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14290,7 +14292,7 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
@@ -14302,10 +14304,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14316,10 +14318,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14345,16 +14347,16 @@
         <v>190</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14382,11 +14384,11 @@
         <v>118</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
       </c>
@@ -14403,7 +14405,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14421,13 +14423,13 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM101" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="AN101" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14438,10 +14440,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14467,16 +14469,16 @@
         <v>190</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14501,14 +14503,14 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
       </c>
@@ -14525,7 +14527,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14543,13 +14545,13 @@
         <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM102" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="AN102" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14560,10 +14562,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14586,17 +14588,17 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14645,7 +14647,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14669,7 +14671,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14680,10 +14682,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14706,13 +14708,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14763,7 +14765,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14784,10 +14786,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14798,10 +14800,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14824,16 +14826,16 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14883,7 +14885,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14904,10 +14906,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14918,10 +14920,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14944,16 +14946,16 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15003,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15024,10 +15026,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15038,10 +15040,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15064,19 +15066,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M107" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15125,7 +15127,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15146,10 +15148,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15160,10 +15162,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15186,13 +15188,13 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15243,7 +15245,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15267,7 +15269,7 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15278,10 +15280,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15310,7 +15312,7 @@
         <v>141</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>143</v>
@@ -15363,7 +15365,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15387,7 +15389,7 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15398,14 +15400,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15427,10 +15429,10 @@
         <v>140</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>143</v>
@@ -15485,7 +15487,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15520,10 +15522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15549,16 +15551,16 @@
         <v>190</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="O111" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15583,14 +15585,14 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y111" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y111" t="s" s="2">
+      <c r="Z111" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z111" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15607,7 +15609,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>94</v>
@@ -15625,16 +15627,16 @@
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AN111" t="s" s="2">
+      <c r="AO111" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -15642,10 +15644,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15668,19 +15670,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="N112" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="O112" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -15729,7 +15731,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15747,27 +15749,27 @@
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AO112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15793,16 +15795,16 @@
         <v>190</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N113" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="O113" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -15827,14 +15829,14 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Y113" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="Y113" t="s" s="2">
+      <c r="Z113" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z113" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
       </c>
@@ -15851,7 +15853,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15860,7 +15862,7 @@
         <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>106</v>
@@ -15875,7 +15877,7 @@
         <v>137</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15886,14 +15888,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15915,16 +15917,16 @@
         <v>190</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15949,14 +15951,14 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="Z114" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
       </c>
@@ -15973,7 +15975,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15991,27 +15993,27 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM114" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM114" t="s" s="2">
+      <c r="AN114" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN114" t="s" s="2">
+      <c r="AO114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16037,16 +16039,16 @@
         <v>84</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16095,7 +16097,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16116,10 +16118,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
